--- a/human_validation/judge/kor/judge_D016_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D016_S001_P002__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,124 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 스미스 선생님입니다. 먼저, 오늘 저를 찾아오시게 된 이유를 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 뭔가 중요한 걸 깜빡했다는 생각이 계속 머릿속에서 떠나질 않아서 왔어요. 예를 들면 이모님 약을 잘못 놔뒀나, 아니면 교실 준비물을 안전하게 정리 안 했나 하는 생각이요. 분명히 제대로 했을 거라는 걸 알면서도, 그 의심이 자꾸만 다시 올라와요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 뭔가를 잊어버렸다는 의심이 들 때, 그걸 없애려고 재차 확인하거나 설명서를 다시 읽거나 다른 사람에게 안심시켜 달라고 하는 행동을 하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네. 집이나 교실을 나서기 전에 같은 걸 몇 번씩 확인해요. 약통, 가스레인지, 수업 계획서 같은 거요. 때로는 그냥 제가 했던 일을 머릿속으로 계속 되짚어보다가 마음이 좀 진정되면 그제야 나가요. 좀 과하다는 건 저도 아는데, 안 그러면 계속 걱정이 되고, 그것 때문에 가끔 늦기도 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 뭔가를 잊어버렸다는 생각이 떠오를 때, 그게 원치 않는데 자꾸 침투해서 사라졌으면 하는 생각처럼 느껴지시나요, 아니면 평소에 걱정하는 방식과 비슷하게 느껴지시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 원치 않는 느낌이에요. 아마 제대로 처리했을 거라는 걸 알면서도, 뭔가 깜빡했다는 생각—이모님 약이나 교실 준비물 같은 거요—이 그냥 계속 머릿속에 다시 떠올라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 지난 2주 동안, 기분이 가라앉거나 평소에 즐기던 일에 대한 흥미나 즐거움이 줄어든 걸 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 아니요, 딱히 기분이 가라앉거나 평소에 즐기던 일에 흥미를 잃었다는 느낌은 못 받았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 뭔가를 잊어버리거나 실수하는 것에 대한 이런 생각 말고도, 건강이나 돈, 가족처럼 삶의 다른 여러 영역에 대해서도 통제하기 힘들 정도로 과도하게 걱정하시는 편인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 그런 것 같진 않아요. 주로 뭔가를 잊어버리거나 실수하는 것에 대한 특정한 걱정이지, 여러 가지가 한꺼번에 다 걱정되는 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>진단명: 강박장애 (D016)
 인구통계: 성별 여성 / 나이 31 / 직업상태 elementary or middle school teacher / 최종학력 대학 재학
@@ -575,173 +684,31 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S065
-배경 서술: 연로한 친척이 왈레스카의 집으로 들어와 함께 살게 되면서, 그녀는 누구도 실망시키지 않으려고 돌봄 업무를 교사 업무, 교회 과외, 살사 수업, 가족 요리 일정 사이에 끼워 넣으려 애썼다. 늘어난 책임 때문에 예전부터 있던 침투적인 의심들을 떨쳐내기가 더 어려워졌는데, 특히 집이나 교실에서 준비를 제대로 했는지에 대한 의심이 심해졌고, 그녀는 한 장소에서 다른 장소로 넘어가기 전에 반복적으로 확인하고 머릿속으로 되짚어보는 행동으로 스스로를 안심시키기 시작했다. 문제는 아직 그녀가 계속 가르치고 사람들과 어울릴 수 있을 정도로는 제한적이었지만, 아침 시간이 느려지고 수업 준비가 힘겨워졌으며 밤에 쓰던 일기도 예전만큼 회복에 도움이 되지 않게 만들었다. 그녀는 스트레스 때문에 찾은 1차 진료 방문에서 이 문제를 언급했고, 담당 의사는 그녀를 정신과 평가로 의뢰했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 스미스 선생님입니다. 먼저, 오늘 저를 찾아오시게 된 이유를 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 뭔가 중요한 걸 깜빡했다는 생각이 계속 머릿속에서 떠나질 않아서 왔어요. 예를 들면 이모님 약을 잘못 놔뒀나, 아니면 교실 준비물을 안전하게 정리 안 했나 하는 생각이요. 분명히 제대로 했을 거라는 걸 알면서도, 그 의심이 자꾸만 다시 올라와요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 뭔가를 잊어버렸다는 의심이 들 때, 그걸 없애려고 재차 확인하거나 설명서를 다시 읽거나 다른 사람에게 안심시켜 달라고 하는 행동을 하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네. 집이나 교실을 나서기 전에 같은 걸 몇 번씩 확인해요. 약통, 가스레인지, 수업 계획서 같은 거요. 때로는 그냥 제가 했던 일을 머릿속으로 계속 되짚어보다가 마음이 좀 진정되면 그제야 나가요. 좀 과하다는 건 저도 아는데, 안 그러면 계속 걱정이 되고, 그것 때문에 가끔 늦기도 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 뭔가를 잊어버렸다는 생각이 떠오를 때, 그게 원치 않는데 자꾸 침투해서 사라졌으면 하는 생각처럼 느껴지시나요, 아니면 평소에 걱정하는 방식과 비슷하게 느껴지시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 원치 않는 느낌이에요. 아마 제대로 처리했을 거라는 걸 알면서도, 뭔가 깜빡했다는 생각—이모님 약이나 교실 준비물 같은 거요—이 그냥 계속 머릿속에 다시 떠올라요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 지난 2주 동안, 기분이 가라앉거나 평소에 즐기던 일에 대한 흥미나 즐거움이 줄어든 걸 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 아니요, 딱히 기분이 가라앉거나 평소에 즐기던 일에 흥미를 잃었다는 느낌은 못 받았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 뭔가를 잊어버리거나 실수하는 것에 대한 이런 생각 말고도, 건강이나 돈, 가족처럼 삶의 다른 여러 영역에 대해서도 통제하기 힘들 정도로 과도하게 걱정하시는 편인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 그런 것 같진 않아요. 주로 뭔가를 잊어버리거나 실수하는 것에 대한 특정한 걱정이지, 여러 가지가 한꺼번에 다 걱정되는 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+배경 서술: 연로한 친척이 왈레스카의 집으로 들어와 함께 살게 되면서, 그녀는 누구도 실망시키지 않으려고 돌봄 업무를 교사 업무, 교회 과외, 살사 수업, 가족 요리 일정 사이에 끼워 넣으려 애썼다. 늘어난 책임 때문에 예전부터 있던 침투적인 의심들을 떨쳐내기가 더 어려워졌는데, 특히 집이나 교실에서 준비를 제대로 했는지에 대한 의심이 심해졌고, 그녀는 한 장소에서 다른 장소로 넘어가기 전에 반복적으로 확인하고 머릿속으로 되짚어보는 행동으로 스스로를 안심시키기 시작했다. 문제는 아직 그녀가 계속 가르치고 사람들과 어울릴 수 있을 정도로는 제한적이었지만, 아침 시간이 느려지고 수업 준비가 힘겨워졌으며 밤에 쓰던 일기도 예전만큼 회복에 도움이 되지 않게 만들었다. 그녀는 스트레스 때문에 찾은 1차 진료 방문에서 이 문제를 언급했고, 담당 의사는 그녀를 정신과 평가로 의뢰했다.
+표집된 증상 목록:
+  - S065 강박사고: 침투적이고 원치 않는 것으로 경험되는 반복적이고 지속적인 생각, 충동, 심상, 그리고 이를 무시하거나 억누르려는 시도.
+  - S066 강박행동: 강박사고에 대한 반응으로, 또는 불안/고통을 예방하기 위해 수행하는 반복적 행동이나 정신적 활동으로, 명백히 과도하거나 현실적으로 연관성이 없음.</t>
+        </is>
+      </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 강박장애 (D016, ICD: F42)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: obsessive_compulsive_symptoms (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 강박사고: 침투적이고 원치 않는 것으로 경험되는 반복적이고 지속적인 생각, 충동, 심상, 그리고 이를 무시하거나 억누르려는 시도.; 강박행동: 강박사고에 대한 반응으로, 또는 불안/고통을 예방하기 위해 수행하는 반복적 행동이나 정신적 활동으로, 명백히 과도하거나 현실적으로 연관성이 없음.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 강박장애 (D016, ICD: F42)
+지속 기간 요건: None
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: obsessive_compulsive_symptoms (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 강박사고: 침투적이고 원치 않는 것으로 경험되는 반복적이고 지속적인 생각, 충동, 심상, 그리고 이를 무시하거나 억누르려는 시도.
+  - 강박행동: 강박사고에 대한 반응으로, 또는 불안/고통을 예방하기 위해 수행하는 반복적 행동이나 정신적 활동으로, 명백히 과도하거나 현실적으로 연관성이 없음.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D016_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D016_S001_P002__claude-sonnet-5_kor.xlsx
@@ -670,6 +670,11 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -704,11 +709,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D016_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D016_S001_P002__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
